--- a/Experiment.xlsx
+++ b/Experiment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abutalib/Projects/personal-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A080382E-5CB8-BD4E-B46B-2A02E6B74FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD0A413-14A3-8A44-88B9-5A1099640035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
   </bookViews>
